--- a/exports/BHARATFORG_full_report.xlsx
+++ b/exports/BHARATFORG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.92</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>742.5</v>
+        <v>724</v>
       </c>
       <c r="I2" t="n">
         <v>736.4137450466104</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.94</v>
+        <v>-5.36</v>
       </c>
       <c r="L2" t="n">
-        <v>4.31</v>
+        <v>6.13</v>
       </c>
       <c r="M2" t="n">
         <v>3.34</v>
       </c>
       <c r="N2" t="n">
-        <v>2.21</v>
+        <v>3.43</v>
       </c>
       <c r="O2" t="n">
         <v>2.52</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>652.95</v>
+        <v>672</v>
       </c>
       <c r="I3" t="n">
         <v>660.0385458217638</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K3" t="n">
-        <v>9.81</v>
+        <v>7.18</v>
       </c>
       <c r="L3" t="n">
         <v>5.94</v>
@@ -612,7 +647,7 @@
         <v>3.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="O3" t="n">
         <v>-3.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.94</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>722</v>
+        <v>710.6</v>
       </c>
       <c r="I4" t="n">
         <v>711.404903529278</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>7.44</v>
+        <v>5.74</v>
       </c>
       <c r="L4" t="n">
         <v>2.21</v>
@@ -669,7 +716,7 @@
         <v>1.22</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="O4" t="n">
         <v>3.58</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.38541666666</v>
+        <v>44697.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>651.15</v>
+        <v>663.4</v>
       </c>
       <c r="I5" t="n">
         <v>653.5172362305401</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>8.369999999999999</v>
+        <v>6.64</v>
       </c>
       <c r="L5" t="n">
         <v>2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.34</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44718.38541666666</v>
+        <v>44718.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>650</v>
+        <v>647.35</v>
       </c>
       <c r="I6" t="n">
         <v>649.9737483932539</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.02</v>
+        <v>-2.42</v>
       </c>
       <c r="L6" t="n">
         <v>3.51</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>655.55</v>
+        <v>672</v>
       </c>
       <c r="I7" t="n">
         <v>667.4039298786621</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.27</v>
+        <v>-3.81</v>
       </c>
       <c r="L7" t="n">
         <v>5.88</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44754.38541666666</v>
+        <v>44754.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>637.35</v>
+        <v>631.4</v>
       </c>
       <c r="I8" t="n">
         <v>634.5753971244038</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.16</v>
+        <v>-6.04</v>
       </c>
       <c r="L8" t="n">
-        <v>5.29</v>
+        <v>6.25</v>
       </c>
       <c r="M8" t="n">
         <v>0.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>6.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>668.75</v>
+        <v>684.95</v>
       </c>
       <c r="I9" t="n">
         <v>672.2982817520108</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.92</v>
+        <v>-8.48</v>
       </c>
       <c r="L9" t="n">
-        <v>6.09</v>
+        <v>9.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0.76</v>
+        <v>1.55</v>
       </c>
       <c r="N9" t="n">
         <v>2.15</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>727.5</v>
+        <v>707.25</v>
       </c>
       <c r="I10" t="n">
         <v>712.9467372796805</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>6.21</v>
+        <v>3.26</v>
       </c>
       <c r="L10" t="n">
         <v>1.96</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.88</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>739.95</v>
+        <v>790.8</v>
       </c>
       <c r="I11" t="n">
         <v>747.976384512619</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.62</v>
+        <v>-11.81</v>
       </c>
       <c r="L11" t="n">
-        <v>4.73</v>
+        <v>12.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7</v>
+        <v>1.36</v>
       </c>
       <c r="N11" t="n">
-        <v>3.49</v>
+        <v>6.74</v>
       </c>
       <c r="O11" t="n">
         <v>-2.36</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.38541666666</v>
+        <v>44792.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>742.95</v>
+        <v>734</v>
       </c>
       <c r="I12" t="n">
         <v>738.8150059591436</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.05</v>
+        <v>-7.18</v>
       </c>
       <c r="L12" t="n">
-        <v>6.71</v>
+        <v>7.39</v>
       </c>
       <c r="M12" t="n">
         <v>0.03</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.86</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44805.55208333334</v>
+        <v>44806.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>752.75</v>
+        <v>763.15</v>
       </c>
       <c r="I13" t="n">
         <v>756.2261568032264</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.55</v>
+        <v>-3.97</v>
       </c>
       <c r="L13" t="n">
-        <v>2.71</v>
+        <v>4.36</v>
       </c>
       <c r="M13" t="n">
         <v>0.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.64</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>784.7</v>
+        <v>750.35</v>
       </c>
       <c r="I14" t="n">
         <v>755.0461360904574</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>2.82</v>
+        <v>-1.68</v>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
         <v>1.54</v>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>4.87</v>
       </c>
       <c r="O14" t="n">
         <v>1.87</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44826.38541666666</v>
+        <v>44826.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>769.3</v>
+        <v>782.95</v>
       </c>
       <c r="I15" t="n">
         <v>781.8277526905575</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.53</v>
+        <v>-4.34</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.77</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>733.7</v>
+        <v>723</v>
       </c>
       <c r="I16" t="n">
         <v>729.9629902073774</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.29</v>
+        <v>-7.66</v>
       </c>
       <c r="L16" t="n">
         <v>9.56</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>706.5</v>
+        <v>762.75</v>
       </c>
       <c r="I17" t="n">
         <v>739.0721441546376</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>2.28</v>
+        <v>-5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>6.92</v>
       </c>
       <c r="M17" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="N17" t="n">
-        <v>2.24</v>
+        <v>7.99</v>
       </c>
       <c r="O17" t="n">
         <v>-3.34</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.59</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44880.55208333334</v>
+        <v>44881.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>854</v>
+        <v>842.3</v>
       </c>
       <c r="I18" t="n">
         <v>850.7247496238957</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>11.96</v>
+        <v>10.43</v>
       </c>
       <c r="L18" t="n">
         <v>5.28</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>837.7</v>
+        <v>876</v>
       </c>
       <c r="I19" t="n">
         <v>869.2137302889438</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>0.55</v>
+        <v>-4</v>
       </c>
       <c r="L19" t="n">
-        <v>2.81</v>
+        <v>4.24</v>
       </c>
       <c r="M19" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>3.86</v>
       </c>
       <c r="O19" t="n">
         <v>-1.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44917.38541666666</v>
+        <v>44917.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>861.15</v>
+        <v>858</v>
       </c>
       <c r="I20" t="n">
         <v>858.0692219754301</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7</v>
+        <v>-2.05</v>
       </c>
       <c r="L20" t="n">
         <v>4.79</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45033.55208333334</v>
+        <v>45034.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>776.4</v>
+        <v>783.5</v>
       </c>
       <c r="I21" t="n">
         <v>781.3493706313758</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>116</v>
+        <v>116.8333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>9.51</v>
+        <v>8.68</v>
       </c>
       <c r="L21" t="n">
         <v>6.06</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45049.55208333334</v>
+        <v>45050.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>784</v>
+        <v>777.3</v>
       </c>
       <c r="I22" t="n">
         <v>778.180724859336</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06</v>
+        <v>-0.79</v>
       </c>
       <c r="L22" t="n">
         <v>1.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.25</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>767.65</v>
+        <v>784.15</v>
       </c>
       <c r="I23" t="n">
         <v>782.1064387964736</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>1.24</v>
+        <v>-0.88</v>
       </c>
       <c r="L23" t="n">
         <v>1.57</v>
       </c>
       <c r="M23" t="n">
-        <v>0.52</v>
+        <v>0.83</v>
       </c>
       <c r="N23" t="n">
-        <v>1.84</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
         <v>-1.15</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.71</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>815.7</v>
+        <v>808.75</v>
       </c>
       <c r="I24" t="n">
         <v>810.9282232763643</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>4.02</v>
+        <v>3.14</v>
       </c>
       <c r="L24" t="n">
         <v>2.28</v>
@@ -1809,7 +2096,7 @@
         <v>0.14</v>
       </c>
       <c r="N24" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="O24" t="n">
         <v>2.29</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45110.38541666666</v>
+        <v>45110.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>838.5</v>
+        <v>840.2</v>
       </c>
       <c r="I25" t="n">
         <v>839.538086480408</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.68</v>
+        <v>-3.89</v>
       </c>
       <c r="L25" t="n">
         <v>4.35</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1076.05</v>
+        <v>1074.95</v>
       </c>
       <c r="I26" t="n">
         <v>1075.400981733517</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>70.83333333333333</v>
+        <v>71</v>
       </c>
       <c r="K26" t="n">
-        <v>28.07</v>
+        <v>27.94</v>
       </c>
       <c r="L26" t="n">
         <v>0.95</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.83</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45184.38541666666</v>
+        <v>45184.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1117.8</v>
+        <v>1133</v>
       </c>
       <c r="I27" t="n">
         <v>1123.975559316265</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.99</v>
+        <v>-5.4</v>
       </c>
       <c r="L27" t="n">
         <v>6.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.82</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1084</v>
+        <v>1058.5</v>
       </c>
       <c r="I28" t="n">
         <v>1074.711276442944</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.32</v>
+        <v>-6.58</v>
       </c>
       <c r="L28" t="n">
-        <v>5.3</v>
+        <v>6.75</v>
       </c>
       <c r="M28" t="n">
         <v>0.32</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.72</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45208.55208333334</v>
+        <v>45209.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1081.75</v>
+        <v>1110.1</v>
       </c>
       <c r="I29" t="n">
         <v>1106.421274398761</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.2</v>
+        <v>-4.87</v>
       </c>
       <c r="L29" t="n">
-        <v>3.42</v>
+        <v>5.42</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>-2.21</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.44</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1096</v>
+        <v>1070.8</v>
       </c>
       <c r="I30" t="n">
         <v>1086.155230554388</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.27</v>
+        <v>-3.54</v>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="M30" t="n">
         <v>0.62</v>
       </c>
       <c r="N30" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="O30" t="n">
         <v>2.84</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1062.65</v>
+        <v>1079</v>
       </c>
       <c r="I31" t="n">
         <v>1070.76896974153</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="L31" t="n">
         <v>2.26</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.54</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1227.3</v>
+        <v>1217.7</v>
       </c>
       <c r="I32" t="n">
         <v>1226.151655449502</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>13.74</v>
+        <v>12.85</v>
       </c>
       <c r="L32" t="n">
         <v>5.93</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1238.5</v>
+        <v>1262.15</v>
       </c>
       <c r="I33" t="n">
         <v>1255.929643954393</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.71</v>
+        <v>-3.65</v>
       </c>
       <c r="L33" t="n">
-        <v>3.15</v>
+        <v>3.97</v>
       </c>
       <c r="M33" t="n">
         <v>1.12</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.86</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1300.7</v>
+        <v>1131.1</v>
       </c>
       <c r="I34" t="n">
         <v>1241.037554163949</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>3.05</v>
+        <v>-10.38</v>
       </c>
       <c r="L34" t="n">
-        <v>2.58</v>
+        <v>11.5</v>
       </c>
       <c r="M34" t="n">
         <v>0.2</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>18.48</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45387.55208333334</v>
+        <v>45390.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1146.8</v>
+        <v>1168</v>
       </c>
       <c r="I35" t="n">
         <v>1167.329949534957</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>53</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.39</v>
+        <v>-3.26</v>
       </c>
       <c r="L35" t="n">
         <v>15.81</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.79</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1246.85</v>
+        <v>1230.35</v>
       </c>
       <c r="I36" t="n">
         <v>1241.699824780203</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K36" t="n">
-        <v>6.75</v>
+        <v>5.34</v>
       </c>
       <c r="L36" t="n">
         <v>2.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.77</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45420.38541666666</v>
+        <v>45420.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1252.3</v>
+        <v>1435</v>
       </c>
       <c r="I37" t="n">
         <v>1300.10606886128</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.78</v>
+        <v>-16.63</v>
       </c>
       <c r="L37" t="n">
-        <v>3.33</v>
+        <v>19.84</v>
       </c>
       <c r="M37" t="n">
         <v>0.72</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>14.42</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1614</v>
+        <v>1469</v>
       </c>
       <c r="I38" t="n">
         <v>1511.928688677647</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>12.47</v>
+        <v>2.37</v>
       </c>
       <c r="L38" t="n">
         <v>12.82</v>
@@ -2607,7 +3062,7 @@
         <v>1.67</v>
       </c>
       <c r="N38" t="n">
-        <v>1.52</v>
+        <v>10.16</v>
       </c>
       <c r="O38" t="n">
         <v>16.37</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1604.3</v>
+        <v>1636</v>
       </c>
       <c r="I39" t="n">
         <v>1617.872404858596</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.37</v>
       </c>
       <c r="L39" t="n">
-        <v>10.24</v>
+        <v>11.98</v>
       </c>
       <c r="M39" t="n">
         <v>2.76</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1668.75</v>
+        <v>1649.5</v>
       </c>
       <c r="I40" t="n">
         <v>1653.34504352983</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="L40" t="n">
         <v>1.89</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.08</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1597.2</v>
+        <v>1686.75</v>
       </c>
       <c r="I41" t="n">
         <v>1672.102799515408</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>3.17</v>
+        <v>-2.26</v>
       </c>
       <c r="L41" t="n">
         <v>2.65</v>
@@ -2778,7 +3269,7 @@
         <v>1.66</v>
       </c>
       <c r="N41" t="n">
-        <v>2.46</v>
+        <v>5.81</v>
       </c>
       <c r="O41" t="n">
         <v>-1.56</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1649.95</v>
+        <v>1571</v>
       </c>
       <c r="I42" t="n">
         <v>1638.194476914553</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.18</v>
+        <v>-6.86</v>
       </c>
       <c r="L42" t="n">
-        <v>4.87</v>
+        <v>8.81</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4</v>
+        <v>4.24</v>
       </c>
       <c r="N42" t="n">
-        <v>3.73</v>
+        <v>6.12</v>
       </c>
       <c r="O42" t="n">
         <v>5.81</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.7</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45601.38541666666</v>
+        <v>45601.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1424.3</v>
+        <v>1458.5</v>
       </c>
       <c r="I43" t="n">
         <v>1438.806225826388</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>92</v>
+        <v>92.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>9.34</v>
+        <v>7.16</v>
       </c>
       <c r="L43" t="n">
         <v>5.34</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.68</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1393.45</v>
+        <v>1363.5</v>
       </c>
       <c r="I44" t="n">
         <v>1381.777236412631</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.46</v>
+        <v>-6.51</v>
       </c>
       <c r="L44" t="n">
-        <v>5.37</v>
+        <v>6.52</v>
       </c>
       <c r="M44" t="n">
         <v>0.32</v>
       </c>
       <c r="N44" t="n">
-        <v>2.15</v>
+        <v>3.66</v>
       </c>
       <c r="O44" t="n">
         <v>2.82</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.53</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1057.9</v>
+        <v>1085.8</v>
       </c>
       <c r="I45" t="n">
         <v>1083.828397789437</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>113.1666666666667</v>
+        <v>114</v>
       </c>
       <c r="K45" t="n">
-        <v>22.41</v>
+        <v>20.37</v>
       </c>
       <c r="L45" t="n">
         <v>2.5</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>7.35</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1150</v>
+        <v>1119.75</v>
       </c>
       <c r="I46" t="n">
         <v>1133.214985287883</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>5.91</v>
+        <v>3.13</v>
       </c>
       <c r="L46" t="n">
         <v>4.95</v>
       </c>
       <c r="M46" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="N46" t="n">
         <v>4.82</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1057.5</v>
+        <v>1072.3</v>
       </c>
       <c r="I47" t="n">
         <v>1060.441950985033</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>5.56</v>
+        <v>4.24</v>
       </c>
       <c r="L47" t="n">
         <v>1.43</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.27</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1307</v>
+        <v>1272.4</v>
       </c>
       <c r="I48" t="n">
         <v>1273.75700837516</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>76</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>21.89</v>
+        <v>18.66</v>
       </c>
       <c r="L48" t="n">
         <v>2.92</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.47</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1137.2</v>
+        <v>1207.6</v>
       </c>
       <c r="I49" t="n">
         <v>1163.78998118824</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K49" t="n">
-        <v>10.63</v>
+        <v>5.09</v>
       </c>
       <c r="L49" t="n">
         <v>5.01</v>
@@ -3234,7 +3821,7 @@
         <v>2.67</v>
       </c>
       <c r="N49" t="n">
-        <v>3.11</v>
+        <v>5.75</v>
       </c>
       <c r="O49" t="n">
         <v>-1.68</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.25</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1251.7</v>
+        <v>1215.3</v>
       </c>
       <c r="I50" t="n">
         <v>1221.70693948436</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>0.64</v>
       </c>
       <c r="L50" t="n">
         <v>5.55</v>
@@ -3291,7 +3890,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>1.31</v>
+        <v>3.17</v>
       </c>
       <c r="O50" t="n">
         <v>5.75</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1220.2</v>
+        <v>1239.2</v>
       </c>
       <c r="I51" t="n">
         <v>1237.632059012747</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.4</v>
+        <v>-1.97</v>
       </c>
       <c r="L51" t="n">
         <v>2.9</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.47</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1403</v>
+        <v>1374.9</v>
       </c>
       <c r="I52" t="n">
         <v>1379.6448312526</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K52" t="n">
-        <v>13.22</v>
+        <v>10.95</v>
       </c>
       <c r="L52" t="n">
         <v>1.73</v>
@@ -3405,7 +4028,7 @@
         <v>0.75</v>
       </c>
       <c r="N52" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="O52" t="n">
         <v>0.8</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.29</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46003.38541666666</v>
+        <v>46003.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1411.6</v>
+        <v>1428</v>
       </c>
       <c r="I53" t="n">
         <v>1426.133161170704</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.67</v>
+        <v>-3.86</v>
       </c>
       <c r="L53" t="n">
-        <v>3.14</v>
+        <v>4.01</v>
       </c>
       <c r="M53" t="n">
         <v>0.49</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.62</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1458</v>
+        <v>1420.3</v>
       </c>
       <c r="I54" t="n">
         <v>1428.85860264253</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>2.1</v>
+        <v>-0.54</v>
       </c>
       <c r="L54" t="n">
         <v>3.08</v>
@@ -3519,7 +4166,7 @@
         <v>0.72</v>
       </c>
       <c r="N54" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
         <v>1.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.73</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1428.6</v>
+        <v>1464</v>
       </c>
       <c r="I55" t="n">
         <v>1447.375431567431</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.58</v>
+        <v>-3.08</v>
       </c>
       <c r="L55" t="n">
-        <v>2.54</v>
+        <v>3.44</v>
       </c>
       <c r="M55" t="n">
         <v>1.27</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1915</v>
+        <v>1813</v>
       </c>
       <c r="I56" t="n">
         <v>1821.992598637832</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K56" t="n">
-        <v>30.81</v>
+        <v>23.84</v>
       </c>
       <c r="L56" t="n">
         <v>9.58</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>10.36</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1669.1</v>
+        <v>1782.2</v>
       </c>
       <c r="I57" t="n">
         <v>1766.939138346842</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K57" t="n">
-        <v>7.94</v>
+        <v>1.7</v>
       </c>
       <c r="L57" t="n">
         <v>5.31</v>
       </c>
       <c r="M57" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="N57" t="n">
-        <v>4.15</v>
+        <v>6.82</v>
       </c>
       <c r="O57" t="n">
         <v>-2.98</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46244.38541666666</v>
+        <v>46244.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>2265</v>
+        <v>2112</v>
       </c>
       <c r="I58" t="n">
         <v>2169.559056214245</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>124</v>
+        <v>124.1666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>27.09</v>
+        <v>18.51</v>
       </c>
       <c r="L58" t="n">
         <v>3.69</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.81</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1910</v>
+        <v>1992.8</v>
       </c>
       <c r="I59" t="n">
         <v>1967.541941371059</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K59" t="n">
-        <v>9.56</v>
+        <v>5.64</v>
       </c>
       <c r="L59" t="n">
         <v>7.38</v>
@@ -3804,7 +4511,7 @@
         <v>1.67</v>
       </c>
       <c r="N59" t="n">
-        <v>2.31</v>
+        <v>3.46</v>
       </c>
       <c r="O59" t="n">
         <v>-6.87</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.96</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1923.3</v>
+        <v>1869.6</v>
       </c>
       <c r="I60" t="n">
         <v>1909.752208749137</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.49</v>
+        <v>-6.18</v>
       </c>
       <c r="L60" t="n">
-        <v>5.08</v>
+        <v>6.77</v>
       </c>
       <c r="M60" t="n">
         <v>1.95</v>
       </c>
       <c r="N60" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="O60" t="n">
         <v>3.46</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,12 @@
       <c r="Q61" t="n">
         <v>34</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6023,7 +6760,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.2</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="6">
@@ -6033,7 +6770,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6780,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="8">
@@ -6053,7 +6790,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="10">
@@ -6073,7 +6810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="11">
@@ -6083,7 +6820,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -6093,7 +6830,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -6103,7 +6840,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="14">
@@ -6113,7 +6850,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.73</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="15">
@@ -6123,7 +6860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.45</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="16">
@@ -6133,7 +6870,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.95</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="17">
@@ -6143,7 +6880,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.81</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="18">
@@ -6153,7 +6890,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="19">
@@ -6163,7 +6900,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.46</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="20">
@@ -6173,7 +6910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -6183,7 +6920,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.81</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="22">
@@ -6193,7 +6930,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6203,7 +6940,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6213,7 +6950,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="25">
@@ -6223,7 +6960,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="26">
@@ -6233,7 +6970,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.49</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="27">
@@ -6253,7 +6990,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
